--- a/customers/matin.xlsx
+++ b/customers/matin.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="53">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -175,6 +175,9 @@
   </si>
   <si>
     <t>لواشک</t>
+  </si>
+  <si>
+    <t>1405/07/01</t>
   </si>
 </sst>
 </file>
@@ -641,7 +644,7 @@
       </c>
       <c r="H2" s="5">
         <f>C54</f>
-        <v>425000</v>
+        <v>-25000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1142,17 +1145,23 @@
     <row r="36" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="9">
         <f t="shared" si="1"/>
-        <v>425000</v>
+        <v>-25000</v>
       </c>
       <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
+      <c r="C36" s="9">
+        <v>450000</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="37" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="9">
         <f t="shared" si="1"/>
-        <v>425000</v>
+        <v>-25000</v>
       </c>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
@@ -1162,7 +1171,7 @@
     <row r="38" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="9">
         <f t="shared" si="1"/>
-        <v>425000</v>
+        <v>-25000</v>
       </c>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -1172,7 +1181,7 @@
     <row r="39" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="9">
         <f t="shared" si="1"/>
-        <v>425000</v>
+        <v>-25000</v>
       </c>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -1182,7 +1191,7 @@
     <row r="40" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="9">
         <f t="shared" si="1"/>
-        <v>425000</v>
+        <v>-25000</v>
       </c>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
@@ -1192,7 +1201,7 @@
     <row r="41" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="9">
         <f t="shared" si="1"/>
-        <v>425000</v>
+        <v>-25000</v>
       </c>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -1202,7 +1211,7 @@
     <row r="42" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="9">
         <f t="shared" si="1"/>
-        <v>425000</v>
+        <v>-25000</v>
       </c>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
@@ -1212,7 +1221,7 @@
     <row r="43" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="9">
         <f t="shared" si="1"/>
-        <v>425000</v>
+        <v>-25000</v>
       </c>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -1222,7 +1231,7 @@
     <row r="44" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="9">
         <f t="shared" si="1"/>
-        <v>425000</v>
+        <v>-25000</v>
       </c>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
@@ -1232,7 +1241,7 @@
     <row r="45" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="9">
         <f t="shared" si="1"/>
-        <v>425000</v>
+        <v>-25000</v>
       </c>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
@@ -1242,7 +1251,7 @@
     <row r="46" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="9">
         <f t="shared" si="1"/>
-        <v>425000</v>
+        <v>-25000</v>
       </c>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -1252,7 +1261,7 @@
     <row r="47" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="9">
         <f t="shared" si="1"/>
-        <v>425000</v>
+        <v>-25000</v>
       </c>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
@@ -1262,7 +1271,7 @@
     <row r="48" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="9">
         <f t="shared" si="1"/>
-        <v>425000</v>
+        <v>-25000</v>
       </c>
       <c r="B48" s="11"/>
       <c r="C48" s="10"/>
@@ -1272,7 +1281,7 @@
     <row r="49" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9">
         <f t="shared" si="1"/>
-        <v>425000</v>
+        <v>-25000</v>
       </c>
       <c r="B49" s="7"/>
       <c r="C49" s="10"/>
@@ -1282,7 +1291,7 @@
     <row r="50" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="9">
         <f t="shared" si="1"/>
-        <v>425000</v>
+        <v>-25000</v>
       </c>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -1292,7 +1301,7 @@
     <row r="51" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="9">
         <f t="shared" si="1"/>
-        <v>425000</v>
+        <v>-25000</v>
       </c>
       <c r="B51" s="9"/>
       <c r="C51" s="9"/>
@@ -1307,7 +1316,7 @@
       </c>
       <c r="C52" s="12">
         <f xml:space="preserve"> SUM(C31:C51)+C24</f>
-        <v>2863000</v>
+        <v>3313000</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="12"/>
@@ -1324,7 +1333,7 @@
       <c r="B54" s="12"/>
       <c r="C54" s="13">
         <f>A51</f>
-        <v>425000</v>
+        <v>-25000</v>
       </c>
       <c r="D54" s="12" t="s">
         <v>6</v>

--- a/customers/matin.xlsx
+++ b/customers/matin.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="55">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -178,6 +178,12 @@
   </si>
   <si>
     <t>1405/07/01</t>
+  </si>
+  <si>
+    <t>1405/07/12</t>
+  </si>
+  <si>
+    <t>چیپس نوشابه تخمه</t>
   </si>
 </sst>
 </file>
@@ -644,7 +650,7 @@
       </c>
       <c r="H2" s="5">
         <f>C54</f>
-        <v>-25000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1161,17 +1167,23 @@
     <row r="37" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="9">
         <f t="shared" si="1"/>
-        <v>-25000</v>
-      </c>
-      <c r="B37" s="9"/>
+        <v>500000</v>
+      </c>
+      <c r="B37" s="9">
+        <v>525000</v>
+      </c>
       <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
+      <c r="D37" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="38" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="9">
         <f t="shared" si="1"/>
-        <v>-25000</v>
+        <v>500000</v>
       </c>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -1181,7 +1193,7 @@
     <row r="39" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="9">
         <f t="shared" si="1"/>
-        <v>-25000</v>
+        <v>500000</v>
       </c>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -1191,7 +1203,7 @@
     <row r="40" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="9">
         <f t="shared" si="1"/>
-        <v>-25000</v>
+        <v>500000</v>
       </c>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
@@ -1201,7 +1213,7 @@
     <row r="41" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="9">
         <f t="shared" si="1"/>
-        <v>-25000</v>
+        <v>500000</v>
       </c>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -1211,7 +1223,7 @@
     <row r="42" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="9">
         <f t="shared" si="1"/>
-        <v>-25000</v>
+        <v>500000</v>
       </c>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
@@ -1221,7 +1233,7 @@
     <row r="43" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="9">
         <f t="shared" si="1"/>
-        <v>-25000</v>
+        <v>500000</v>
       </c>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -1231,7 +1243,7 @@
     <row r="44" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="9">
         <f t="shared" si="1"/>
-        <v>-25000</v>
+        <v>500000</v>
       </c>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
@@ -1241,7 +1253,7 @@
     <row r="45" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="9">
         <f t="shared" si="1"/>
-        <v>-25000</v>
+        <v>500000</v>
       </c>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
@@ -1251,7 +1263,7 @@
     <row r="46" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="9">
         <f t="shared" si="1"/>
-        <v>-25000</v>
+        <v>500000</v>
       </c>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -1261,7 +1273,7 @@
     <row r="47" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="9">
         <f t="shared" si="1"/>
-        <v>-25000</v>
+        <v>500000</v>
       </c>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
@@ -1271,7 +1283,7 @@
     <row r="48" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="9">
         <f t="shared" si="1"/>
-        <v>-25000</v>
+        <v>500000</v>
       </c>
       <c r="B48" s="11"/>
       <c r="C48" s="10"/>
@@ -1281,7 +1293,7 @@
     <row r="49" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9">
         <f t="shared" si="1"/>
-        <v>-25000</v>
+        <v>500000</v>
       </c>
       <c r="B49" s="7"/>
       <c r="C49" s="10"/>
@@ -1291,7 +1303,7 @@
     <row r="50" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="9">
         <f t="shared" si="1"/>
-        <v>-25000</v>
+        <v>500000</v>
       </c>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -1301,7 +1313,7 @@
     <row r="51" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="9">
         <f t="shared" si="1"/>
-        <v>-25000</v>
+        <v>500000</v>
       </c>
       <c r="B51" s="9"/>
       <c r="C51" s="9"/>
@@ -1312,7 +1324,7 @@
       <c r="A52" s="12"/>
       <c r="B52" s="12">
         <f xml:space="preserve"> SUM(B31:B51)+B24</f>
-        <v>3288000</v>
+        <v>3813000</v>
       </c>
       <c r="C52" s="12">
         <f xml:space="preserve"> SUM(C31:C51)+C24</f>
@@ -1333,7 +1345,7 @@
       <c r="B54" s="12"/>
       <c r="C54" s="13">
         <f>A51</f>
-        <v>-25000</v>
+        <v>500000</v>
       </c>
       <c r="D54" s="12" t="s">
         <v>6</v>

--- a/customers/matin.xlsx
+++ b/customers/matin.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="57">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -184,6 +184,12 @@
   </si>
   <si>
     <t>چیپس نوشابه تخمه</t>
+  </si>
+  <si>
+    <t>1405/07/19</t>
+  </si>
+  <si>
+    <t>الباقی سیگار</t>
   </si>
 </sst>
 </file>
@@ -650,7 +656,7 @@
       </c>
       <c r="H2" s="5">
         <f>C54</f>
-        <v>500000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1183,17 +1189,23 @@
     <row r="38" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="9">
         <f t="shared" si="1"/>
-        <v>500000</v>
-      </c>
-      <c r="B38" s="9"/>
+        <v>600000</v>
+      </c>
+      <c r="B38" s="9">
+        <v>100000</v>
+      </c>
       <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
+      <c r="D38" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="39" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="9">
         <f t="shared" si="1"/>
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -1203,7 +1215,7 @@
     <row r="40" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="9">
         <f t="shared" si="1"/>
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
@@ -1213,7 +1225,7 @@
     <row r="41" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="9">
         <f t="shared" si="1"/>
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -1223,7 +1235,7 @@
     <row r="42" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="9">
         <f t="shared" si="1"/>
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
@@ -1233,7 +1245,7 @@
     <row r="43" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="9">
         <f t="shared" si="1"/>
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -1243,7 +1255,7 @@
     <row r="44" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="9">
         <f t="shared" si="1"/>
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
@@ -1253,7 +1265,7 @@
     <row r="45" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="9">
         <f t="shared" si="1"/>
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
@@ -1263,7 +1275,7 @@
     <row r="46" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="9">
         <f t="shared" si="1"/>
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -1273,7 +1285,7 @@
     <row r="47" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="9">
         <f t="shared" si="1"/>
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
@@ -1283,7 +1295,7 @@
     <row r="48" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="9">
         <f t="shared" si="1"/>
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="B48" s="11"/>
       <c r="C48" s="10"/>
@@ -1293,7 +1305,7 @@
     <row r="49" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9">
         <f t="shared" si="1"/>
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="B49" s="7"/>
       <c r="C49" s="10"/>
@@ -1303,7 +1315,7 @@
     <row r="50" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="9">
         <f t="shared" si="1"/>
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -1313,7 +1325,7 @@
     <row r="51" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="9">
         <f t="shared" si="1"/>
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="B51" s="9"/>
       <c r="C51" s="9"/>
@@ -1324,7 +1336,7 @@
       <c r="A52" s="12"/>
       <c r="B52" s="12">
         <f xml:space="preserve"> SUM(B31:B51)+B24</f>
-        <v>3813000</v>
+        <v>3913000</v>
       </c>
       <c r="C52" s="12">
         <f xml:space="preserve"> SUM(C31:C51)+C24</f>
@@ -1345,7 +1357,7 @@
       <c r="B54" s="12"/>
       <c r="C54" s="13">
         <f>A51</f>
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="D54" s="12" t="s">
         <v>6</v>

--- a/customers/matin.xlsx
+++ b/customers/matin.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="59">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -190,6 +190,12 @@
   </si>
   <si>
     <t>الباقی سیگار</t>
+  </si>
+  <si>
+    <t>1405/07/24</t>
+  </si>
+  <si>
+    <t>سیگار فندک</t>
   </si>
 </sst>
 </file>
@@ -656,7 +662,7 @@
       </c>
       <c r="H2" s="5">
         <f>C54</f>
-        <v>600000</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1205,17 +1211,23 @@
     <row r="39" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="9">
         <f t="shared" si="1"/>
-        <v>600000</v>
-      </c>
-      <c r="B39" s="9"/>
+        <v>800000</v>
+      </c>
+      <c r="B39" s="9">
+        <v>200000</v>
+      </c>
       <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
+      <c r="D39" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="40" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="9">
         <f t="shared" si="1"/>
-        <v>600000</v>
+        <v>800000</v>
       </c>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
@@ -1225,7 +1237,7 @@
     <row r="41" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="9">
         <f t="shared" si="1"/>
-        <v>600000</v>
+        <v>800000</v>
       </c>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -1235,7 +1247,7 @@
     <row r="42" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="9">
         <f t="shared" si="1"/>
-        <v>600000</v>
+        <v>800000</v>
       </c>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
@@ -1245,7 +1257,7 @@
     <row r="43" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="9">
         <f t="shared" si="1"/>
-        <v>600000</v>
+        <v>800000</v>
       </c>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -1255,7 +1267,7 @@
     <row r="44" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="9">
         <f t="shared" si="1"/>
-        <v>600000</v>
+        <v>800000</v>
       </c>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
@@ -1265,7 +1277,7 @@
     <row r="45" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="9">
         <f t="shared" si="1"/>
-        <v>600000</v>
+        <v>800000</v>
       </c>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
@@ -1275,7 +1287,7 @@
     <row r="46" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="9">
         <f t="shared" si="1"/>
-        <v>600000</v>
+        <v>800000</v>
       </c>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -1285,7 +1297,7 @@
     <row r="47" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="9">
         <f t="shared" si="1"/>
-        <v>600000</v>
+        <v>800000</v>
       </c>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
@@ -1295,7 +1307,7 @@
     <row r="48" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="9">
         <f t="shared" si="1"/>
-        <v>600000</v>
+        <v>800000</v>
       </c>
       <c r="B48" s="11"/>
       <c r="C48" s="10"/>
@@ -1305,7 +1317,7 @@
     <row r="49" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9">
         <f t="shared" si="1"/>
-        <v>600000</v>
+        <v>800000</v>
       </c>
       <c r="B49" s="7"/>
       <c r="C49" s="10"/>
@@ -1315,7 +1327,7 @@
     <row r="50" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="9">
         <f t="shared" si="1"/>
-        <v>600000</v>
+        <v>800000</v>
       </c>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -1325,7 +1337,7 @@
     <row r="51" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="9">
         <f t="shared" si="1"/>
-        <v>600000</v>
+        <v>800000</v>
       </c>
       <c r="B51" s="9"/>
       <c r="C51" s="9"/>
@@ -1336,7 +1348,7 @@
       <c r="A52" s="12"/>
       <c r="B52" s="12">
         <f xml:space="preserve"> SUM(B31:B51)+B24</f>
-        <v>3913000</v>
+        <v>4113000</v>
       </c>
       <c r="C52" s="12">
         <f xml:space="preserve"> SUM(C31:C51)+C24</f>
@@ -1357,7 +1369,7 @@
       <c r="B54" s="12"/>
       <c r="C54" s="13">
         <f>A51</f>
-        <v>600000</v>
+        <v>800000</v>
       </c>
       <c r="D54" s="12" t="s">
         <v>6</v>

--- a/customers/matin.xlsx
+++ b/customers/matin.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="60">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -196,6 +196,9 @@
   </si>
   <si>
     <t>سیگار فندک</t>
+  </si>
+  <si>
+    <t>1405/07/26</t>
   </si>
 </sst>
 </file>
@@ -662,7 +665,7 @@
       </c>
       <c r="H2" s="5">
         <f>C54</f>
-        <v>800000</v>
+        <v>927000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1227,17 +1230,23 @@
     <row r="40" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="9">
         <f t="shared" si="1"/>
-        <v>800000</v>
-      </c>
-      <c r="B40" s="9"/>
+        <v>927000</v>
+      </c>
+      <c r="B40" s="9">
+        <v>127000</v>
+      </c>
       <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
+      <c r="D40" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="41" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="9">
         <f t="shared" si="1"/>
-        <v>800000</v>
+        <v>927000</v>
       </c>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -1247,7 +1256,7 @@
     <row r="42" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="9">
         <f t="shared" si="1"/>
-        <v>800000</v>
+        <v>927000</v>
       </c>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
@@ -1257,7 +1266,7 @@
     <row r="43" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="9">
         <f t="shared" si="1"/>
-        <v>800000</v>
+        <v>927000</v>
       </c>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -1267,7 +1276,7 @@
     <row r="44" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="9">
         <f t="shared" si="1"/>
-        <v>800000</v>
+        <v>927000</v>
       </c>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
@@ -1277,7 +1286,7 @@
     <row r="45" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="9">
         <f t="shared" si="1"/>
-        <v>800000</v>
+        <v>927000</v>
       </c>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
@@ -1287,7 +1296,7 @@
     <row r="46" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="9">
         <f t="shared" si="1"/>
-        <v>800000</v>
+        <v>927000</v>
       </c>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -1297,7 +1306,7 @@
     <row r="47" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="9">
         <f t="shared" si="1"/>
-        <v>800000</v>
+        <v>927000</v>
       </c>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
@@ -1307,7 +1316,7 @@
     <row r="48" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="9">
         <f t="shared" si="1"/>
-        <v>800000</v>
+        <v>927000</v>
       </c>
       <c r="B48" s="11"/>
       <c r="C48" s="10"/>
@@ -1317,7 +1326,7 @@
     <row r="49" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9">
         <f t="shared" si="1"/>
-        <v>800000</v>
+        <v>927000</v>
       </c>
       <c r="B49" s="7"/>
       <c r="C49" s="10"/>
@@ -1327,7 +1336,7 @@
     <row r="50" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="9">
         <f t="shared" si="1"/>
-        <v>800000</v>
+        <v>927000</v>
       </c>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -1337,7 +1346,7 @@
     <row r="51" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="9">
         <f t="shared" si="1"/>
-        <v>800000</v>
+        <v>927000</v>
       </c>
       <c r="B51" s="9"/>
       <c r="C51" s="9"/>
@@ -1348,7 +1357,7 @@
       <c r="A52" s="12"/>
       <c r="B52" s="12">
         <f xml:space="preserve"> SUM(B31:B51)+B24</f>
-        <v>4113000</v>
+        <v>4240000</v>
       </c>
       <c r="C52" s="12">
         <f xml:space="preserve"> SUM(C31:C51)+C24</f>
@@ -1369,7 +1378,7 @@
       <c r="B54" s="12"/>
       <c r="C54" s="13">
         <f>A51</f>
-        <v>800000</v>
+        <v>927000</v>
       </c>
       <c r="D54" s="12" t="s">
         <v>6</v>

--- a/customers/matin.xlsx
+++ b/customers/matin.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="61">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -199,6 +199,9 @@
   </si>
   <si>
     <t>1405/07/26</t>
+  </si>
+  <si>
+    <t>1405/07/30</t>
   </si>
 </sst>
 </file>
@@ -665,7 +668,7 @@
       </c>
       <c r="H2" s="5">
         <f>C54</f>
-        <v>927000</v>
+        <v>-3000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1246,17 +1249,23 @@
     <row r="41" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="9">
         <f t="shared" si="1"/>
-        <v>927000</v>
+        <v>-3000</v>
       </c>
       <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
+      <c r="C41" s="9">
+        <v>930000</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="42" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="9">
         <f t="shared" si="1"/>
-        <v>927000</v>
+        <v>-3000</v>
       </c>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
@@ -1266,7 +1275,7 @@
     <row r="43" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="9">
         <f t="shared" si="1"/>
-        <v>927000</v>
+        <v>-3000</v>
       </c>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -1276,7 +1285,7 @@
     <row r="44" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="9">
         <f t="shared" si="1"/>
-        <v>927000</v>
+        <v>-3000</v>
       </c>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
@@ -1286,7 +1295,7 @@
     <row r="45" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="9">
         <f t="shared" si="1"/>
-        <v>927000</v>
+        <v>-3000</v>
       </c>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
@@ -1296,7 +1305,7 @@
     <row r="46" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="9">
         <f t="shared" si="1"/>
-        <v>927000</v>
+        <v>-3000</v>
       </c>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -1306,7 +1315,7 @@
     <row r="47" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="9">
         <f t="shared" si="1"/>
-        <v>927000</v>
+        <v>-3000</v>
       </c>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
@@ -1316,7 +1325,7 @@
     <row r="48" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="9">
         <f t="shared" si="1"/>
-        <v>927000</v>
+        <v>-3000</v>
       </c>
       <c r="B48" s="11"/>
       <c r="C48" s="10"/>
@@ -1326,7 +1335,7 @@
     <row r="49" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9">
         <f t="shared" si="1"/>
-        <v>927000</v>
+        <v>-3000</v>
       </c>
       <c r="B49" s="7"/>
       <c r="C49" s="10"/>
@@ -1336,7 +1345,7 @@
     <row r="50" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="9">
         <f t="shared" si="1"/>
-        <v>927000</v>
+        <v>-3000</v>
       </c>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -1346,7 +1355,7 @@
     <row r="51" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="9">
         <f t="shared" si="1"/>
-        <v>927000</v>
+        <v>-3000</v>
       </c>
       <c r="B51" s="9"/>
       <c r="C51" s="9"/>
@@ -1361,7 +1370,7 @@
       </c>
       <c r="C52" s="12">
         <f xml:space="preserve"> SUM(C31:C51)+C24</f>
-        <v>3313000</v>
+        <v>4243000</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="12"/>
@@ -1378,7 +1387,7 @@
       <c r="B54" s="12"/>
       <c r="C54" s="13">
         <f>A51</f>
-        <v>927000</v>
+        <v>-3000</v>
       </c>
       <c r="D54" s="12" t="s">
         <v>6</v>
